--- a/docs/adjudicacion-definitivo-02.xlsx
+++ b/docs/adjudicacion-definitivo-02.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Adjudicación" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Registro" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Adjudicación" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registro" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5781,7 +5781,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Paciente disconforme con el resultado estético de una cicatriz tras una intervención abdominal programada, sin ninguna complicación clínica asociada. Ha enviado un correo solicitando una compensación económica y amenaza con dejar reseñas negativas si no recibe respuesta en la semana. El consentimiento firmado menciona de forma genérica la posibilidad de cicatrización visible, pero no incluye fotografías de referencia ni una conversación documentada sobre expectativas estéticas. Se pide una lectura rápida del riesgo real detrás de este reclamo.</t>
+          <t>Paciente intervenido por colecistectomía que evolucionó con una lesión de la vía biliar detectada recién en el control postoperatorio, lo que obligó a una segunda intervención de urgencia. La familia ha solicitado una explicación formal por escrito y menciona la posibilidad de iniciar un reclamo. La documentación del procedimiento original está completa, pero no hay registro claro de la conversación previa sobre este riesgo específico. Se busca orientación sobre exposición legal y sobre cómo proceder con la respuesta a la familia.</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -5791,26 +5791,26 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Abg. Julio Aliaga Cornejo</t>
+          <t>Abg. Karina Sotelo Delgado</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Derecho Sanitario, Consentimiento Informado</t>
+          <t>Seguros Médicos, Consentimiento Informado</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Reumatología</t>
+          <t>Psiquiatría</t>
         </is>
       </c>
       <c r="H120" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I120" s="6" t="n"/>
       <c r="J120" s="6" t="n"/>
@@ -6177,36 +6177,36 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Paciente con diabetes de larga data que desarrolló una complicación relacionada con un ajuste tardío de su tratamiento, tras varias consultas de endocrinología en las que, según refiere, no se revisaron a fondo sus controles metabólicos recientes. La familia ha solicitado una explicación sobre por qué no se intensificó el manejo antes, y menciona que estaría dispuesta a buscar una segunda opinión legal si no queda satisfecha. La historia clínica muestra los controles registrados, pero no un análisis explícito de la tendencia entre consultas. Se solicita una lectura del riesgo del caso.</t>
+          <t>Gestante con parto instrumentado que presentó hemorragia post-parto severa, requirió transfusión de múltiples unidades y permaneció 48 horas en cuidados intensivos. El esposo ha exigido una reunión con la dirección médica y ha mencionado a un abogado externo que ya está revisando el caso. El consentimiento para el parto instrumentado está firmado, pero no detalla el riesgo de hemorragia mayor. Se requiere asesoría urgente sobre cómo documentar lo ocurrido y qué comunicar a la familia antes de esa reunión.</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Endocrinología</t>
+          <t>Ginecología y Obstetricia</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Critica</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Abg. Daniela Vargas Solís</t>
+          <t>Abg. Iván Contreras Sotelo</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Derecho Sanitario, Consentimiento Informado</t>
+          <t>Derecho Penal Médico, Bioética y Derecho</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Ginecología y Obstetricia, Pediatría</t>
+          <t>Neurología, Psiquiatría</t>
         </is>
       </c>
       <c r="H129" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="I129" s="6" t="n"/>
       <c r="J129" s="6" t="n"/>
@@ -6615,12 +6615,12 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>Consulta ambulatoria de rutina en la que el paciente refiere no haber recibido la llamada de seguimiento acordada tras un resultado de laboratorio limítrofe. No hubo daño ni complicación clínica, pero el paciente se ha quejado formalmente por la falta de comunicación y pide una explicación por escrito. La historia clínica registra el resultado y la indicación de seguimiento, pero no hay evidencia de que la llamada se haya realizado. Se pide orientación sobre cómo responder al reclamo sin reconocer una falta que no está clara.</t>
+          <t>Paciente al que se le indicó un nuevo tratamiento farmacológico para una arritmia sin que, según refiere, se le explicaran con claridad los efectos secundarios más relevantes ni las alternativas disponibles. No ha habido ninguna complicación clínica, pero el paciente se siente insatisfecho con el nivel de información recibido y ha pedido una copia de su historia clínica para revisarla con un tercero. El registro de la consulta es breve y no detalla explícitamente la conversación sobre riesgos del nuevo medicamento. Se pide una lectura preventiva del caso.</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Medicina General</t>
+          <t>Cardiología</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -6630,21 +6630,21 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Abg. Julio Aliaga Cornejo</t>
+          <t>Abg. Diana Landa Ochoa</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Derecho Sanitario, Consentimiento Informado</t>
+          <t>Responsabilidad Civil Médica, Derecho Médico</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Reumatología</t>
+          <t>Pediatría, Medicina General</t>
         </is>
       </c>
       <c r="H139" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="I139" s="6" t="n"/>
       <c r="J139" s="6" t="n"/>
@@ -7659,12 +7659,12 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>Paciente al que se le indicó un nuevo tratamiento farmacológico para una arritmia sin que, según refiere, se le explicaran con claridad los efectos secundarios más relevantes ni las alternativas disponibles. No ha habido ninguna complicación clínica, pero el paciente se siente insatisfecho con el nivel de información recibido y ha pedido una copia de su historia clínica para revisarla con un tercero. El registro de la consulta es breve y no detalla explícitamente la conversación sobre riesgos del nuevo medicamento. Se pide una lectura preventiva del caso.</t>
+          <t>Consulta ambulatoria de rutina en la que el paciente refiere no haber recibido la llamada de seguimiento acordada tras un resultado de laboratorio limítrofe. No hubo daño ni complicación clínica, pero el paciente se ha quejado formalmente por la falta de comunicación y pide una explicación por escrito. La historia clínica registra el resultado y la indicación de seguimiento, pero no hay evidencia de que la llamada se haya realizado. Se pide orientación sobre cómo responder al reclamo sin reconocer una falta que no está clara.</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Cardiología</t>
+          <t>Medicina General</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -7674,21 +7674,21 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Abg. Silvia Ríos Contreras</t>
+          <t>Abg. Pilar Zevallos Farfán</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Consentimiento Informado, Derecho Sanitario</t>
+          <t>Derecho Sanitario, Bioética y Derecho</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Oftalmología</t>
+          <t>Gastroenterología</t>
         </is>
       </c>
       <c r="H163" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I163" s="6" t="n"/>
       <c r="J163" s="6" t="n"/>
@@ -8043,36 +8043,36 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>Paciente disconforme con el resultado estético de una cicatriz tras una intervención abdominal programada, sin ninguna complicación clínica asociada. Ha enviado un correo solicitando una compensación económica y amenaza con dejar reseñas negativas si no recibe respuesta en la semana. El consentimiento firmado menciona de forma genérica la posibilidad de cicatrización visible, pero no incluye fotografías de referencia ni una conversación documentada sobre expectativas estéticas. Se pide una lectura rápida del riesgo real detrás de este reclamo.</t>
+          <t>Paciente politraumatizado por una caída que permaneció varias horas en el área de emergencias antes de recibir atención especializada, en un día de alta demanda del servicio. La familia reclama que esa demora agravó una lesión que inicialmente parecía menor y que terminó requiriendo cirugía. El registro de triaje documenta la hora de ingreso, pero no hay una nota clara que explique el motivo específico de la demora en la atención especializada. Se solicita una evaluación de la exposición legal derivada de este caso.</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Cirugía General</t>
+          <t>Traumatología</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Abg. Fernando Zúñiga Palacios</t>
+          <t>Abg. Renato Salazar Méndez</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Negligencia Médica, Responsabilidad Civil Médica</t>
+          <t>Seguros Médicos, Responsabilidad Civil Médica, Derecho Médico</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Traumatología, Cirugía General</t>
+          <t>Traumatología, Cirugía General, Anestesiología</t>
         </is>
       </c>
       <c r="H172" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I172" s="6" t="n"/>
       <c r="J172" s="6" t="n"/>
@@ -8259,12 +8259,12 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>Paciente politraumatizado por una caída que permaneció varias horas en el área de emergencias antes de recibir atención especializada, en un día de alta demanda del servicio. La familia reclama que esa demora agravó una lesión que inicialmente parecía menor y que terminó requiriendo cirugía. El registro de triaje documenta la hora de ingreso, pero no hay una nota clara que explique el motivo específico de la demora en la atención especializada. Se solicita una evaluación de la exposición legal derivada de este caso.</t>
+          <t>Paciente sometido a un cateterismo que presentó una disección coronaria durante el procedimiento, resuelta con un stent adicional no previsto originalmente. La recuperación fue favorable, pero la familia cuestiona por qué no se les informó de inmediato sobre la complicación y se enteraron recién al día siguiente por otro miembro del equipo. El consentimiento cubre el procedimiento base pero no detalla explícitamente el riesgo de disección. Se solicita asesoría sobre la exposición derivada del retraso en la comunicación, más que del evento clínico en sí.</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Traumatología</t>
+          <t>Cardiología</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -8469,22 +8469,22 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>Paciente politraumatizado por una caída que permaneció varias horas en el área de emergencias antes de recibir atención especializada, en un día de alta demanda del servicio. La familia reclama que esa demora agravó una lesión que inicialmente parecía menor y que terminó requiriendo cirugía. El registro de triaje documenta la hora de ingreso, pero no hay una nota clara que explique el motivo específico de la demora en la atención especializada. Se solicita una evaluación de la exposición legal derivada de este caso.</t>
+          <t>Paciente que sufrió una perforación durante una colonoscopía diagnóstica, resuelta quirúrgicamente sin secuelas mayores tras una estadía hospitalaria breve. El paciente entiende que es una complicación reconocida del procedimiento, pero cuestiona que no se le haya explicado con suficiente claridad antes de firmar el consentimiento, que menciona el riesgo de forma muy general. No ha habido amenaza explícita de demanda, pero sí ha solicitado copia completa del expediente y una reunión con el especialista. Se pide una opinión preliminar sobre el nivel de riesgo.</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Traumatología</t>
+          <t>Gastroenterología</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Abg. Daniela Vargas Solís</t>
+          <t>Abg. Camila Delgado Escobar</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -8494,11 +8494,11 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Ginecología y Obstetricia, Pediatría</t>
+          <t>Gastroenterología</t>
         </is>
       </c>
       <c r="H182" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I182" s="6" t="n"/>
       <c r="J182" s="6" t="n"/>
@@ -8553,36 +8553,36 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>Paciente sometido a un cateterismo que presentó una disección coronaria durante el procedimiento, resuelta con un stent adicional no previsto originalmente. La recuperación fue favorable, pero la familia cuestiona por qué no se les informó de inmediato sobre la complicación y se enteraron recién al día siguiente por otro miembro del equipo. El consentimiento cubre el procedimiento base pero no detalla explícitamente el riesgo de disección. Se solicita asesoría sobre la exposición derivada del retraso en la comunicación, más que del evento clínico en sí.</t>
+          <t>Paciente con síntomas articulares persistentes que fue derivado a reumatología después de varios meses de consultas en otras especialidades sin un diagnóstico claro, y que finalmente fue diagnosticado con una enfermedad autoinmune en una etapa ya establecida. El paciente cuestiona si ese tiempo pudo haberse acortado y solicita una revisión de su historial completo. No hay evidencia de un error puntual, sino de una serie de consultas en las que el cuadro no terminaba de encajar en un diagnóstico. Se pide una opinión sobre si existe algún fundamento para un reclamo formal.</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Cardiología</t>
+          <t>Reumatología</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Abg. Mateo Huamán Ríos</t>
+          <t>Abg. Álvaro Farfán Aliaga</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Derecho Penal Médico, Bioética y Derecho</t>
+          <t>Derecho Penal Médico, Negligencia Médica</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Anestesiología, Cirugía General</t>
+          <t>Cirugía General, Traumatología</t>
         </is>
       </c>
       <c r="H184" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I184" s="6" t="n"/>
       <c r="J184" s="6" t="n"/>
@@ -8895,22 +8895,22 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>Paciente con un hallazgo radiológico sospechoso que permaneció sin biopsia confirmatoria durante casi dos meses por una serie de citas reprogramadas y pérdida de una orden médica en el sistema. El diagnóstico finalmente confirmado corresponde a un estadio más avanzado que el que hubiera correspondido de haberse actuado antes. El paciente y su familia han solicitado formalmente el expediente completo y mencionan estar evaluando asesoría legal externa. Se pide apoyo para reconstruir la cronología exacta de las reprogramaciones antes de responder a esa solicitud.</t>
+          <t>Paciente con diabetes de larga data que desarrolló una complicación relacionada con un ajuste tardío de su tratamiento, tras varias consultas de endocrinología en las que, según refiere, no se revisaron a fondo sus controles metabólicos recientes. La familia ha solicitado una explicación sobre por qué no se intensificó el manejo antes, y menciona que estaría dispuesta a buscar una segunda opinión legal si no queda satisfecha. La historia clínica muestra los controles registrados, pero no un análisis explícito de la tendencia entre consultas. Se solicita una lectura del riesgo del caso.</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Oncología</t>
+          <t>Endocrinología</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Abg. Rocío Ochoa Manrique</t>
+          <t>Abg. Beatriz Salcedo Otiniano</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -8920,11 +8920,11 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Oncología</t>
+          <t>Cardiología</t>
         </is>
       </c>
       <c r="H192" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I192" s="6" t="n"/>
       <c r="J192" s="6" t="n"/>
@@ -8985,17 +8985,17 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>Paciente con fractura de tobillo tratada de forma conservadora que terminó consolidando en mala posición, lo que ha requerido una cirugía correctiva meses después. El paciente sostiene que nunca se le explicó la alternativa quirúrgica inicial y que de haberlo sabido la habría preferido. Se trata de un caso de traumatología con documentación parcial: existe la radiografía inicial pero no una nota explícita sobre las opciones discutidas con el paciente en esa primera consulta. Se solicita evaluación del nivel de exposición legal.</t>
+          <t>Paciente sometido a un cateterismo que presentó una disección coronaria durante el procedimiento, resuelta con un stent adicional no previsto originalmente. La recuperación fue favorable, pero la familia cuestiona por qué no se les informó de inmediato sobre la complicación y se enteraron recién al día siguiente por otro miembro del equipo. El consentimiento cubre el procedimiento base pero no detalla explícitamente el riesgo de disección. Se solicita asesoría sobre la exposición derivada del retraso en la comunicación, más que del evento clínico en sí.</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Traumatología</t>
+          <t>Cardiología</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -9159,12 +9159,12 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>Consulta ambulatoria de rutina en la que el paciente refiere no haber recibido la llamada de seguimiento acordada tras un resultado de laboratorio limítrofe. No hubo daño ni complicación clínica, pero el paciente se ha quejado formalmente por la falta de comunicación y pide una explicación por escrito. La historia clínica registra el resultado y la indicación de seguimiento, pero no hay evidencia de que la llamada se haya realizado. Se pide orientación sobre cómo responder al reclamo sin reconocer una falta que no está clara.</t>
+          <t>Paciente que se sometió a un procedimiento estético ambulatorio menor y desarrolló una reacción cutánea localizada que se resolvió sin secuelas tras un tratamiento tópico. No hubo ninguna hospitalización ni complicación grave, pero el paciente ha expresado su malestar por no haber sido advertido de este riesgo específico antes del procedimiento, y ha pedido que se revise su expediente. El consentimiento firmado es un formato genérico que no detalla reacciones cutáneas particulares. Se pide una opinión rápida sobre si amerita alguna acción adicional.</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Medicina General</t>
+          <t>Dermatología</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -9174,21 +9174,21 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Abg. Diego Huamán Vera</t>
+          <t>Abg. Mateo Huamán Ríos</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Derecho Penal Médico, Responsabilidad Civil Médica, Derecho Sanitario</t>
+          <t>Derecho Penal Médico, Bioética y Derecho</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Neurología, Psiquiatría, Medicina General</t>
+          <t>Anestesiología, Cirugía General</t>
         </is>
       </c>
       <c r="H198" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I198" s="6" t="n"/>
       <c r="J198" s="6" t="n"/>
@@ -9201,36 +9201,36 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>Paciente que sufrió una perforación durante una colonoscopía diagnóstica, resuelta quirúrgicamente sin secuelas mayores tras una estadía hospitalaria breve. El paciente entiende que es una complicación reconocida del procedimiento, pero cuestiona que no se le haya explicado con suficiente claridad antes de firmar el consentimiento, que menciona el riesgo de forma muy general. No ha habido amenaza explícita de demanda, pero sí ha solicitado copia completa del expediente y una reunión con el especialista. Se pide una opinión preliminar sobre el nivel de riesgo.</t>
+          <t>Paciente con resultados de laboratorio compatibles con un trastorno hematológico que tardaron en derivarse a la especialidad correspondiente debido a una interconsulta que quedó pendiente en el sistema durante varias semanas. El diagnóstico finalmente se confirmó y el tratamiento se inició, pero con un retraso que el paciente considera evitable. No ha habido una complicación clínica grave hasta el momento, pero el paciente ha solicitado una explicación formal sobre lo ocurrido con la interconsulta. Se pide una valoración de la exposición legal antes de responder por escrito.</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Gastroenterología</t>
+          <t>Hematología</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Abg. Camila Delgado Escobar</t>
+          <t>Abg. Mateo Huamán Ríos</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Derecho Sanitario, Consentimiento Informado</t>
+          <t>Derecho Penal Médico, Bioética y Derecho</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Gastroenterología</t>
+          <t>Anestesiología, Cirugía General</t>
         </is>
       </c>
       <c r="H199" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="I199" s="6" t="n"/>
       <c r="J199" s="6" t="n"/>
@@ -9327,36 +9327,36 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>Paciente sometido a un cateterismo que presentó una disección coronaria durante el procedimiento, resuelta con un stent adicional no previsto originalmente. La recuperación fue favorable, pero la familia cuestiona por qué no se les informó de inmediato sobre la complicación y se enteraron recién al día siguiente por otro miembro del equipo. El consentimiento cubre el procedimiento base pero no detalla explícitamente el riesgo de disección. Se solicita asesoría sobre la exposición derivada del retraso en la comunicación, más que del evento clínico en sí.</t>
+          <t>Paciente con síntomas articulares persistentes que fue derivado a reumatología después de varios meses de consultas en otras especialidades sin un diagnóstico claro, y que finalmente fue diagnosticado con una enfermedad autoinmune en una etapa ya establecida. El paciente cuestiona si ese tiempo pudo haberse acortado y solicita una revisión de su historial completo. No hay evidencia de un error puntual, sino de una serie de consultas en las que el cuadro no terminaba de encajar en un diagnóstico. Se pide una opinión sobre si existe algún fundamento para un reclamo formal.</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Cardiología</t>
+          <t>Reumatología</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Abg. Mateo Huamán Ríos</t>
+          <t>Abg. Andrés Villanueva Bravo</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Derecho Penal Médico, Bioética y Derecho</t>
+          <t>Derecho Médico, Responsabilidad Civil Médica</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Anestesiología, Cirugía General</t>
+          <t>Reumatología</t>
         </is>
       </c>
       <c r="H202" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I202" s="6" t="n"/>
       <c r="J202" s="6" t="n"/>
@@ -9795,7 +9795,7 @@
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>Paciente politraumatizado por una caída que permaneció varias horas en el área de emergencias antes de recibir atención especializada, en un día de alta demanda del servicio. La familia reclama que esa demora agravó una lesión que inicialmente parecía menor y que terminó requiriendo cirugía. El registro de triaje documenta la hora de ingreso, pero no hay una nota clara que explique el motivo específico de la demora en la atención especializada. Se solicita una evaluación de la exposición legal derivada de este caso.</t>
+          <t>Paciente con fractura de tobillo tratada de forma conservadora que terminó consolidando en mala posición, lo que ha requerido una cirugía correctiva meses después. El paciente sostiene que nunca se le explicó la alternativa quirúrgica inicial y que de haberlo sabido la habría preferido. Se trata de un caso de traumatología con documentación parcial: existe la radiografía inicial pero no una nota explícita sobre las opciones discutidas con el paciente en esa primera consulta. Se solicita evaluación del nivel de exposición legal.</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -9805,26 +9805,26 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Abg. Valeria Aguirre Bocanegra</t>
+          <t>Abg. Iván Contreras Sotelo</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Responsabilidad Civil Médica, Bioética y Derecho</t>
+          <t>Derecho Penal Médico, Bioética y Derecho</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Oncología, Hematología</t>
+          <t>Neurología, Psiquiatría</t>
         </is>
       </c>
       <c r="H213" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I213" s="6" t="n"/>
       <c r="J213" s="6" t="n"/>
@@ -9879,36 +9879,36 @@
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>Paciente dado de alta del servicio de psiquiatría tras una hospitalización breve, que días después tuvo una crisis que requirió una nueva internación de emergencia. La familia cuestiona que el alta se haya dado sin una evaluación de riesgo suficientemente documentada, y ha solicitado por escrito una revisión del criterio clínico utilizado. La historia clínica registra la evaluación de alta, pero de forma breve y sin una escala de riesgo estandarizada aplicada. Se requiere orientación sobre cómo abordar esta solicitud sin reconocer una falla que no está establecida.</t>
+          <t>Paciente politraumatizado por una caída que permaneció varias horas en el área de emergencias antes de recibir atención especializada, en un día de alta demanda del servicio. La familia reclama que esa demora agravó una lesión que inicialmente parecía menor y que terminó requiriendo cirugía. El registro de triaje documenta la hora de ingreso, pero no hay una nota clara que explique el motivo específico de la demora en la atención especializada. Se solicita una evaluación de la exposición legal derivada de este caso.</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Psiquiatría</t>
+          <t>Traumatología</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Abg. Iván Contreras Sotelo</t>
+          <t>Abg. Teresa Alvarado Yupanqui</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Derecho Penal Médico, Bioética y Derecho</t>
+          <t>Derecho Sanitario, Consentimiento Informado</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Neurología, Psiquiatría</t>
+          <t>Endocrinología</t>
         </is>
       </c>
       <c r="H215" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="I215" s="6" t="n"/>
       <c r="J215" s="6" t="n"/>
@@ -9927,12 +9927,12 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>Paciente disconforme con el resultado estético de una cicatriz tras una intervención abdominal programada, sin ninguna complicación clínica asociada. Ha enviado un correo solicitando una compensación económica y amenaza con dejar reseñas negativas si no recibe respuesta en la semana. El consentimiento firmado menciona de forma genérica la posibilidad de cicatrización visible, pero no incluye fotografías de referencia ni una conversación documentada sobre expectativas estéticas. Se pide una lectura rápida del riesgo real detrás de este reclamo.</t>
+          <t>Paciente al que se le indicó un nuevo tratamiento farmacológico para una arritmia sin que, según refiere, se le explicaran con claridad los efectos secundarios más relevantes ni las alternativas disponibles. No ha habido ninguna complicación clínica, pero el paciente se siente insatisfecho con el nivel de información recibido y ha pedido una copia de su historia clínica para revisarla con un tercero. El registro de la consulta es breve y no detalla explícitamente la conversación sobre riesgos del nuevo medicamento. Se pide una lectura preventiva del caso.</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Cirugía General</t>
+          <t>Cardiología</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -9942,21 +9942,21 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Abg. Mateo Huamán Ríos</t>
+          <t>Abg. Elena Marín Bedoya</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Derecho Penal Médico, Bioética y Derecho</t>
+          <t>Negligencia Médica, Bioética y Derecho</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Anestesiología, Cirugía General</t>
+          <t>Cardiología, Neurología</t>
         </is>
       </c>
       <c r="H216" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I216" s="6" t="n"/>
       <c r="J216" s="6" t="n"/>
